--- a/artfynd/A 20335-2021 artfynd.xlsx
+++ b/artfynd/A 20335-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125856096</v>
       </c>
       <c r="B2" t="n">
-        <v>106695</v>
+        <v>106702</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>125856073</v>
       </c>
       <c r="B3" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20335-2021 artfynd.xlsx
+++ b/artfynd/A 20335-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125856096</v>
       </c>
       <c r="B2" t="n">
-        <v>106702</v>
+        <v>106703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>125856073</v>
       </c>
       <c r="B3" t="n">
-        <v>100513</v>
+        <v>100514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20335-2021 artfynd.xlsx
+++ b/artfynd/A 20335-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125856096</v>
       </c>
       <c r="B2" t="n">
-        <v>106703</v>
+        <v>106705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>125856073</v>
       </c>
       <c r="B3" t="n">
-        <v>100514</v>
+        <v>100516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20335-2021 artfynd.xlsx
+++ b/artfynd/A 20335-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125856096</v>
       </c>
       <c r="B2" t="n">
-        <v>106705</v>
+        <v>106709</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>125856073</v>
       </c>
       <c r="B3" t="n">
-        <v>100516</v>
+        <v>100520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20335-2021 artfynd.xlsx
+++ b/artfynd/A 20335-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125856096</v>
       </c>
       <c r="B2" t="n">
-        <v>106709</v>
+        <v>106710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>125856073</v>
       </c>
       <c r="B3" t="n">
-        <v>100520</v>
+        <v>100521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20335-2021 artfynd.xlsx
+++ b/artfynd/A 20335-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125856096</v>
       </c>
       <c r="B2" t="n">
-        <v>106710</v>
+        <v>106712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>125856073</v>
       </c>
       <c r="B3" t="n">
-        <v>100521</v>
+        <v>100523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20335-2021 artfynd.xlsx
+++ b/artfynd/A 20335-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125856096</v>
       </c>
       <c r="B2" t="n">
-        <v>106712</v>
+        <v>106714</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>125856073</v>
       </c>
       <c r="B3" t="n">
-        <v>100523</v>
+        <v>100525</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20335-2021 artfynd.xlsx
+++ b/artfynd/A 20335-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125856096</v>
       </c>
       <c r="B2" t="n">
-        <v>106714</v>
+        <v>106718</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>125856073</v>
       </c>
       <c r="B3" t="n">
-        <v>100525</v>
+        <v>100527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20335-2021 artfynd.xlsx
+++ b/artfynd/A 20335-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125856096</v>
       </c>
       <c r="B2" t="n">
-        <v>106718</v>
+        <v>106731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>125856073</v>
       </c>
       <c r="B3" t="n">
-        <v>100527</v>
+        <v>100531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20335-2021 artfynd.xlsx
+++ b/artfynd/A 20335-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125856096</v>
       </c>
       <c r="B2" t="n">
-        <v>106731</v>
+        <v>106734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>125856073</v>
       </c>
       <c r="B3" t="n">
-        <v>100531</v>
+        <v>100534</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20335-2021 artfynd.xlsx
+++ b/artfynd/A 20335-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125856096</v>
       </c>
       <c r="B2" t="n">
-        <v>106734</v>
+        <v>106743</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>125856073</v>
       </c>
       <c r="B3" t="n">
-        <v>100534</v>
+        <v>100543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
